--- a/基金/观察基金/009608_广发中证500指数增强A/009608_交易记录.xlsx
+++ b/基金/观察基金/009608_广发中证500指数增强A/009608_交易记录.xlsx
@@ -1670,7 +1670,7 @@
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="list" sqref="D2:D84">
-      <formula1>"买入,卖出"</formula1>
+      <formula1>"买入,卖出,转入"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
